--- a/Gimbal/pitch.xlsx
+++ b/Gimbal/pitch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RM\testwork\2025_Infantry\Infantry_crossing_hole\2026_pancake_car\Gimbal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCB69D5-F35E-476F-A5AA-96BF2B02CE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE9ADDD-E806-49FB-A80E-3F0AAF876B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
   <si>
     <t>pitch</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,86 +69,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;2.89</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;-0.12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;-2.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;-4.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;-5.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;-6.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;-8.17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;13.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;-13.47</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;-13.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;-12.25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;-11.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;-10.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;-7.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;-6.7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;-5.20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>&gt;-4.7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>&gt;-3.44</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;9.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;11.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>边界角度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -193,10 +117,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>T=529.9058 sinθ+1764.462cosθ+150.68168sgnω</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下降</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -210,6 +130,90 @@
   </si>
   <si>
     <t>T2=G+C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;-6.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;-4.53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;-2.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;3.66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;0.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;7.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;10.78</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;-11.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;-10.78</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;-9.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;-8.23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;-7.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;-6.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;-6.26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;-5.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;-3.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;15.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;16.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;24.78</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;26.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T=606.6655 sinθ+1723.191cosθ+153.83098sgnω</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -438,64 +442,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>-8.2878097245096178</c:v>
+                  <c:v>-6.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-6.75</c:v>
+                  <c:v>-4.53</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5.8</c:v>
+                  <c:v>-2.12</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.9000000000000004</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-2.4</c:v>
+                  <c:v>3.66</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.12</c:v>
+                  <c:v>7.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.89</c:v>
+                  <c:v>10.78</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13.6</c:v>
+                  <c:v>-11.3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-13.47</c:v>
+                  <c:v>-10.78</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-13.3</c:v>
+                  <c:v>-9</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-12.25</c:v>
+                  <c:v>-8.23</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-11.75</c:v>
+                  <c:v>-7.8</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-10.5</c:v>
+                  <c:v>-6.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-7.75</c:v>
+                  <c:v>-6.26</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-6.7</c:v>
+                  <c:v>-5.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-5.2</c:v>
+                  <c:v>-4.7</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-4.7</c:v>
+                  <c:v>-3.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-3.44</c:v>
+                  <c:v>15.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.8000000000000007</c:v>
+                  <c:v>16.899999999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>11.8</c:v>
+                  <c:v>24.78</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1554,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="9" max="9" width="10.46484375" customWidth="1"/>
@@ -1568,162 +1572,161 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>1500</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <f>E3-8.17</f>
-        <v>-8.2878097245096178</v>
+        <v>-6.2</v>
       </c>
       <c r="E2">
         <f>RADIANS(D2)</f>
-        <v>-0.14464956747149701</v>
+        <v>-0.10821041362364843</v>
       </c>
       <c r="F2">
         <f>SIN(E2)</f>
-        <v>-0.14414566578901128</v>
+        <v>-0.10799935570602284</v>
       </c>
       <c r="G2">
         <f>COS(E2)</f>
-        <v>0.98955647996172647</v>
+        <v>0.99415096397231539</v>
       </c>
       <c r="H2">
         <f>IF(C2="&lt;",-1,1)</f>
         <v>-1</v>
       </c>
       <c r="I2" cm="1">
-        <f t="array" ref="I2:L6">LINEST(B2:B21,F2:H21,FALSE,TRUE)</f>
-        <v>150.68168319934588</v>
+        <f t="array" ref="I2:L6">LINEST(B2:B22,F2:H22,FALSE,TRUE)</f>
+        <v>153.83098311545623</v>
       </c>
       <c r="J2">
-        <v>1764.4620083949717</v>
+        <v>1723.191382134451</v>
       </c>
       <c r="K2">
-        <v>529.90578713808259</v>
+        <v>606.66550803237124</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>1525</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>-6.75</v>
+        <v>-4.53</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E21" si="0">RADIANS(D3)</f>
-        <v>-0.11780972450961724</v>
+        <f t="shared" ref="E3:E22" si="0">RADIANS(D3)</f>
+        <v>-7.9063415115343136E-2</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F21" si="1">SIN(E3)</f>
-        <v>-0.11753739745783764</v>
+        <f t="shared" ref="F3:F22" si="1">SIN(E3)</f>
+        <v>-7.8981069644306456E-2</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G21" si="2">COS(E3)</f>
-        <v>0.99306845695492629</v>
+        <f t="shared" ref="G3:G22" si="2">COS(E3)</f>
+        <v>0.99687611599327686</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H21" si="3">IF(C3="&lt;",-1,1)</f>
+        <f t="shared" ref="H3:H22" si="3">IF(C3="&lt;",-1,1)</f>
         <v>-1</v>
       </c>
       <c r="I3">
-        <v>5.2554868350899815</v>
+        <v>7.5856182856258467</v>
       </c>
       <c r="J3">
-        <v>5.6568635065686586</v>
+        <v>7.7441649980394835</v>
       </c>
       <c r="K3">
-        <v>38.1424473368157</v>
+        <v>36.987603852356891</v>
       </c>
       <c r="L3" t="e">
         <v>#N/A</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>1550</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>-5.8</v>
+        <v>-2.12</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>-0.10122909661567112</v>
+        <v>-3.7000980142279788E-2</v>
       </c>
       <c r="F4">
         <f t="shared" si="1"/>
-        <v>-0.10105629718294634</v>
+        <v>-3.6992537882611969E-2</v>
       </c>
       <c r="G4">
         <f t="shared" si="2"/>
-        <v>0.99488070882878821</v>
+        <v>0.99931554182900784</v>
       </c>
       <c r="H4">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>0.99986166617446715</v>
+        <v>0.99969971990545103</v>
       </c>
       <c r="J4">
-        <v>22.241762528000038</v>
+        <v>32.877105658113116</v>
       </c>
       <c r="K4" t="e">
         <v>#N/A</v>
@@ -1734,38 +1737,38 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>1575</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>-4.9000000000000004</v>
+        <v>0.75</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>-8.5521133347722156E-2</v>
+        <v>1.3089969389957472E-2</v>
       </c>
       <c r="F5">
         <f t="shared" si="1"/>
-        <v>-8.541692313736747E-2</v>
+        <v>1.3089595571344441E-2</v>
       </c>
       <c r="G5">
         <f t="shared" si="2"/>
-        <v>0.99634529619090639</v>
+        <v>0.999914327574007</v>
       </c>
       <c r="H5">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>40958.04300334541</v>
+        <v>19975.344447793981</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" t="e">
         <v>#N/A</v>
@@ -1776,38 +1779,38 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>1600</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>-2.4</v>
+        <v>3.66</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>-4.1887902047863905E-2</v>
+        <v>6.387905062299247E-2</v>
       </c>
       <c r="F6">
         <f t="shared" si="1"/>
-        <v>-4.1875653729199623E-2</v>
+        <v>6.3835616055581398E-2</v>
       </c>
       <c r="G6">
         <f t="shared" si="2"/>
-        <v>0.99912283009885838</v>
+        <v>0.99796042713266164</v>
       </c>
       <c r="H6">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>60785340.167994015</v>
+        <v>64774293.726623818</v>
       </c>
       <c r="J6">
-        <v>8409.832005983093</v>
+        <v>19456.273376185203</v>
       </c>
       <c r="K6" t="e">
         <v>#N/A</v>
@@ -1818,28 +1821,28 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>1625</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>-0.12</v>
+        <v>7.8</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>-2.0943951023931952E-3</v>
+        <v>0.1361356816555577</v>
       </c>
       <c r="F7">
         <f t="shared" si="1"/>
-        <v>-2.0943935712193738E-3</v>
+        <v>0.13571557243430438</v>
       </c>
       <c r="G7">
         <f t="shared" si="2"/>
-        <v>0.9999978067553793</v>
+        <v>0.9907478404714436</v>
       </c>
       <c r="H7">
         <f t="shared" si="3"/>
@@ -1848,70 +1851,70 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>1650</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>2.89</v>
+        <v>10.78</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>5.0440015382636129E-2</v>
+        <v>0.1881464933649887</v>
       </c>
       <c r="F8">
         <f t="shared" si="1"/>
-        <v>5.0418629896161082E-2</v>
+        <v>0.18703842024225384</v>
       </c>
       <c r="G8">
         <f t="shared" si="2"/>
-        <v>0.99872817210660181</v>
+        <v>0.98235259930092411</v>
       </c>
       <c r="H8">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>1675</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>13.6</v>
+        <v>-11.3</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0.23736477827122882</v>
+        <v>-0.19722220547535926</v>
       </c>
       <c r="F9">
         <f t="shared" si="1"/>
-        <v>0.23514211310259001</v>
+        <v>-0.19594614424251772</v>
       </c>
       <c r="G9">
         <f t="shared" si="2"/>
-        <v>0.97196100057854629</v>
+        <v>0.98061465854661301</v>
       </c>
       <c r="H9">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1920,28 +1923,28 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>1700</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>-13.47</v>
+        <v>-10.78</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>-0.23509585024363619</v>
+        <v>-0.1881464933649887</v>
       </c>
       <c r="F10">
         <f t="shared" si="1"/>
-        <v>-0.23293620017923489</v>
+        <v>-0.18703842024225384</v>
       </c>
       <c r="G10">
         <f t="shared" si="2"/>
-        <v>0.9724920188084113</v>
+        <v>0.98235259930092411</v>
       </c>
       <c r="H10">
         <f t="shared" si="3"/>
@@ -1950,28 +1953,28 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>1725</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>-13.3</v>
+        <v>-9</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>-0.23212879051524585</v>
+        <v>-0.15707963267948966</v>
       </c>
       <c r="F11">
         <f t="shared" si="1"/>
-        <v>-0.23004973718810443</v>
+        <v>-0.15643446504023087</v>
       </c>
       <c r="G11">
         <f t="shared" si="2"/>
-        <v>0.97317887277708826</v>
+        <v>0.98768834059513777</v>
       </c>
       <c r="H11">
         <f t="shared" si="3"/>
@@ -1980,28 +1983,28 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>1750</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>-12.25</v>
+        <v>-8.23</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>-0.21380283336930536</v>
+        <v>-0.14364059743913332</v>
       </c>
       <c r="F12">
         <f t="shared" si="1"/>
-        <v>-0.21217767215644626</v>
+        <v>-0.14314715975318573</v>
       </c>
       <c r="G12">
         <f t="shared" si="2"/>
-        <v>0.97723110646267886</v>
+        <v>0.9897014148997646</v>
       </c>
       <c r="H12">
         <f t="shared" si="3"/>
@@ -2010,28 +2013,28 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>1775</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>-11.75</v>
+        <v>-7.8</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>-0.20507618710933373</v>
+        <v>-0.1361356816555577</v>
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
-        <v>-0.20364175114017749</v>
+        <v>-0.13571557243430438</v>
       </c>
       <c r="G13">
         <f t="shared" si="2"/>
-        <v>0.97904547248458385</v>
+        <v>0.9907478404714436</v>
       </c>
       <c r="H13">
         <f t="shared" si="3"/>
@@ -2040,28 +2043,28 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B14">
         <v>1800</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>-10.5</v>
+        <v>-6.8</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>-0.18325957145940461</v>
+        <v>-0.11868238913561441</v>
       </c>
       <c r="F14">
         <f t="shared" si="1"/>
-        <v>-0.18223552549214747</v>
+        <v>-0.11840396830650095</v>
       </c>
       <c r="G14">
         <f t="shared" si="2"/>
-        <v>0.98325490756395462</v>
+        <v>0.99296550810653694</v>
       </c>
       <c r="H14">
         <f t="shared" si="3"/>
@@ -2070,28 +2073,28 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>1825</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>-7.75</v>
+        <v>-6.26</v>
       </c>
       <c r="E15">
         <f t="shared" si="0"/>
-        <v>-0.13526301702956053</v>
+        <v>-0.10925761117484503</v>
       </c>
       <c r="F15">
         <f t="shared" si="1"/>
-        <v>-0.134850930273723</v>
+        <v>-0.1090403687534694</v>
       </c>
       <c r="G15">
         <f t="shared" si="2"/>
-        <v>0.99086589738688224</v>
+        <v>0.99403732222794705</v>
       </c>
       <c r="H15">
         <f t="shared" si="3"/>
@@ -2100,28 +2103,28 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>1850</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>-6.7</v>
+        <v>-5.6</v>
       </c>
       <c r="E16">
         <f t="shared" si="0"/>
-        <v>-0.11693705988362008</v>
+        <v>-9.7738438111682452E-2</v>
       </c>
       <c r="F16">
         <f t="shared" si="1"/>
-        <v>-0.11667073709933316</v>
+        <v>-9.7582899759149466E-2</v>
       </c>
       <c r="G16">
         <f t="shared" si="2"/>
-        <v>0.99317064953848611</v>
+        <v>0.99522739998183118</v>
       </c>
       <c r="H16">
         <f t="shared" si="3"/>
@@ -2130,28 +2133,28 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B17">
         <v>1875</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="E17">
         <f t="shared" si="0"/>
-        <v>-9.0757121103705138E-2</v>
+        <v>-8.2030474843733492E-2</v>
       </c>
       <c r="F17">
         <f t="shared" si="1"/>
-        <v>-9.0632580197780158E-2</v>
+        <v>-8.1938508630040929E-2</v>
       </c>
       <c r="G17">
         <f t="shared" si="2"/>
-        <v>0.99588439861597033</v>
+        <v>0.9966373868180366</v>
       </c>
       <c r="H17">
         <f t="shared" si="3"/>
@@ -2160,28 +2163,28 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B18">
         <v>1900</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>-4.7</v>
+        <v>-3.5</v>
       </c>
       <c r="E18">
         <f t="shared" si="0"/>
-        <v>-8.2030474843733492E-2</v>
+        <v>-6.1086523819801536E-2</v>
       </c>
       <c r="F18">
         <f t="shared" si="1"/>
-        <v>-8.1938508630040929E-2</v>
+        <v>-6.1048539534856873E-2</v>
       </c>
       <c r="G18">
         <f t="shared" si="2"/>
-        <v>0.9966373868180366</v>
+        <v>0.99813479842186692</v>
       </c>
       <c r="H18">
         <f t="shared" si="3"/>
@@ -2190,28 +2193,28 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B19">
         <v>1925</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>-3.44</v>
+        <v>15.5</v>
       </c>
       <c r="E19">
         <f t="shared" si="0"/>
-        <v>-6.0039326268604934E-2</v>
+        <v>0.27052603405912107</v>
       </c>
       <c r="F19">
         <f t="shared" si="1"/>
-        <v>-6.0003261935620736E-2</v>
+        <v>0.26723837607825685</v>
       </c>
       <c r="G19">
         <f t="shared" si="2"/>
-        <v>0.99819818100269309</v>
+        <v>0.96363045320862295</v>
       </c>
       <c r="H19">
         <f t="shared" si="3"/>
@@ -2220,28 +2223,28 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B20">
         <v>1950</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>9.8000000000000007</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E20">
         <f t="shared" si="0"/>
-        <v>0.17104226669544431</v>
+        <v>0.29496064358704166</v>
       </c>
       <c r="F20">
         <f t="shared" si="1"/>
-        <v>0.17020949916603256</v>
+        <v>0.29070219359825245</v>
       </c>
       <c r="G20">
         <f t="shared" si="2"/>
-        <v>0.98540789848349009</v>
+        <v>0.95681358405760741</v>
       </c>
       <c r="H20">
         <f t="shared" si="3"/>
@@ -2250,30 +2253,60 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B21">
         <v>1975</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>11.8</v>
+        <v>24.78</v>
       </c>
       <c r="E21">
         <f t="shared" si="0"/>
-        <v>0.2059488517353309</v>
+        <v>0.43249258864419488</v>
       </c>
       <c r="F21">
         <f t="shared" si="1"/>
-        <v>0.20449605184179034</v>
+        <v>0.41913518278061318</v>
       </c>
       <c r="G21">
         <f t="shared" si="2"/>
-        <v>0.978867388761685</v>
+        <v>0.90792383962282985</v>
       </c>
       <c r="H21">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22">
+        <v>2000</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>26.7</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>0.46600291028248597</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>0.44931899861589658</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="2"/>
+        <v>0.89337138832783758</v>
+      </c>
+      <c r="H22">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>

--- a/Gimbal/pitch.xlsx
+++ b/Gimbal/pitch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RM\testwork\2025_Infantry\Infantry_crossing_hole\2026_pancake_car\Gimbal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE9ADDD-E806-49FB-A80E-3F0AAF876B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777B0681-029B-4962-B77B-3099074F0217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -221,7 +221,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +231,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -257,11 +266,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1259,15 +1269,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>376239</xdr:colOff>
+      <xdr:colOff>57151</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>147636</xdr:rowOff>
+      <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>64296</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>109538</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1849,7 +1859,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1883,8 +1893,11 @@
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" ht="15" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1913,13 +1926,13 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
@@ -2312,9 +2325,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:M9"/>
+  <mergeCells count="1">
+    <mergeCell ref="I8:N8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
